--- a/data/trans_dic/P62A$otras-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P62A$otras-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que recibe otro tipo de pensión</t>
+          <t>Población que percibe otro tipo de pensión (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,89</t>
+          <t>0,0; 2,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,33; 10,29</t>
+          <t>3,23; 9,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 10,44</t>
+          <t>2,82; 10,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,61; 28,09</t>
+          <t>16,65; 27,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 9,0</t>
+          <t>1,43; 8,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,15; 16,39</t>
+          <t>5,76; 16,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,85; 17,82</t>
+          <t>6,98; 18,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,5; 22,19</t>
+          <t>13,83; 22,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,22</t>
+          <t>0,7; 4,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,45; 11,76</t>
+          <t>5,16; 10,87</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,4; 11,81</t>
+          <t>5,78; 12,02</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,39; 23,42</t>
+          <t>16,47; 23,46</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 2,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,77; 14,05</t>
+          <t>5,47; 13,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 10,42</t>
+          <t>4,44; 10,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,2; 37,34</t>
+          <t>25,95; 37,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 9,48</t>
+          <t>1,51; 9,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,82; 20,24</t>
+          <t>9,6; 20,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,94; 20,2</t>
+          <t>9,57; 20,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,8; 24,34</t>
+          <t>15,06; 23,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,72</t>
+          <t>0,77; 4,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,53; 14,92</t>
+          <t>8,47; 15,03</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,62; 13,3</t>
+          <t>7,64; 13,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,2; 29,08</t>
+          <t>21,88; 29,53</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,67</t>
+          <t>0,0; 4,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 12,88</t>
+          <t>3,59; 12,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,52; 11,43</t>
+          <t>3,5; 10,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26,45; 39,1</t>
+          <t>26,13; 38,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 12,79</t>
+          <t>3,12; 12,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,07; 21,28</t>
+          <t>8,46; 20,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,43; 16,57</t>
+          <t>5,84; 16,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 24,88</t>
+          <t>2,52; 25,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 6,31</t>
+          <t>1,77; 6,2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,93; 13,92</t>
+          <t>7,25; 14,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,2; 11,17</t>
+          <t>5,24; 11,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,83; 30,1</t>
+          <t>6,94; 30,08</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,64</t>
+          <t>0,45; 3,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 8,8</t>
+          <t>2,98; 9,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,08; 10,76</t>
+          <t>4,21; 10,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,02; 39,86</t>
+          <t>29,34; 39,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,17; 8,75</t>
+          <t>1,87; 9,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,51; 17,29</t>
+          <t>9,14; 18,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,74; 25,31</t>
+          <t>14,26; 24,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,85; 27,04</t>
+          <t>18,47; 26,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,17</t>
+          <t>1,55; 5,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,33; 12,25</t>
+          <t>6,55; 12,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,11; 16,17</t>
+          <t>10,49; 16,53</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,88; 31,72</t>
+          <t>25,07; 31,66</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,74</t>
+          <t>0,38; 1,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 8,9</t>
+          <t>5,23; 8,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,91; 8,29</t>
+          <t>4,98; 8,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27,24; 33,18</t>
+          <t>27,09; 33,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,74</t>
+          <t>3,0; 6,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,5; 15,47</t>
+          <t>10,42; 15,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,16; 17,48</t>
+          <t>12,25; 17,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,28; 21,49</t>
+          <t>8,34; 21,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,53</t>
+          <t>1,83; 3,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,17; 11,3</t>
+          <t>8,13; 11,32</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,71; 12,01</t>
+          <t>8,88; 11,91</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,7; 26,17</t>
+          <t>14,67; 26,29</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que recibe otro tipo de pensión</t>
+          <t>Población que percibe otro tipo de pensión (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4947</t>
+          <t>0; 4008</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7046; 21750</t>
+          <t>6833; 21040</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5925; 19774</t>
+          <t>5337; 20230</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29895; 50545</t>
+          <t>29963; 48650</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1806; 11398</t>
+          <t>1805; 11075</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10092; 26885</t>
+          <t>9456; 26344</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10216; 26572</t>
+          <t>10413; 26896</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22960; 37746</t>
+          <t>23524; 37743</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2677; 12578</t>
+          <t>2091; 12220</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20482; 44151</t>
+          <t>19379; 40809</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18274; 40007</t>
+          <t>19579; 40695</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>57372; 81997</t>
+          <t>57666; 82135</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4572</t>
+          <t>0; 4973</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14203; 34605</t>
+          <t>13461; 32512</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10822; 27584</t>
+          <t>11736; 28496</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51927; 74000</t>
+          <t>51430; 74794</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2529; 14538</t>
+          <t>2318; 14156</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20600; 42445</t>
+          <t>20130; 42420</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20260; 41173</t>
+          <t>19504; 41233</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29149; 44901</t>
+          <t>27779; 44059</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2639; 13988</t>
+          <t>2880; 15412</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38875; 68021</t>
+          <t>38642; 68532</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35711; 62328</t>
+          <t>35804; 63348</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>84935; 111284</t>
+          <t>83703; 112992</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7207</t>
+          <t>0; 7256</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5775; 21738</t>
+          <t>6061; 20444</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6409; 20814</t>
+          <t>6380; 20002</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53133; 78535</t>
+          <t>52485; 77287</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3642; 15323</t>
+          <t>3741; 15508</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13411; 31466</t>
+          <t>12513; 30543</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7349; 22442</t>
+          <t>7910; 22106</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7485; 86474</t>
+          <t>8746; 88724</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4795; 17294</t>
+          <t>4863; 16988</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21936; 44075</t>
+          <t>22945; 45969</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16517; 35464</t>
+          <t>16637; 36485</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>37450; 165040</t>
+          <t>38077; 164933</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>854; 6920</t>
+          <t>848; 6985</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7230; 21540</t>
+          <t>7290; 22547</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10806; 28518</t>
+          <t>11167; 26980</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>64571; 88686</t>
+          <t>65278; 88463</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3825; 15424</t>
+          <t>3291; 15858</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19105; 38813</t>
+          <t>20512; 40878</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36643; 62928</t>
+          <t>35453; 62020</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>44401; 63680</t>
+          <t>43493; 63543</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6071; 18930</t>
+          <t>5688; 18758</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29690; 57463</t>
+          <t>30736; 56739</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51943; 83070</t>
+          <t>53862; 84910</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>113953; 145290</t>
+          <t>114835; 145004</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2732; 12874</t>
+          <t>2795; 13718</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>45598; 77561</t>
+          <t>45583; 76997</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44216; 74670</t>
+          <t>44849; 75868</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>218331; 265915</t>
+          <t>217117; 264657</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18477; 38851</t>
+          <t>17283; 39179</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>78344; 115435</t>
+          <t>77718; 118426</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89612; 128867</t>
+          <t>90297; 132020</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>77601; 201462</t>
+          <t>78212; 203284</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23706; 46446</t>
+          <t>23990; 48784</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>132079; 182666</t>
+          <t>131474; 183044</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>142716; 196679</t>
+          <t>145433; 195121</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>255724; 455137</t>
+          <t>255174; 457237</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P62A$otras-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P62A$otras-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,34</t>
+          <t>0,0; 3,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,23; 9,95</t>
+          <t>3,15; 10,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,82; 10,68</t>
+          <t>2,99; 10,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,65; 27,03</t>
+          <t>17,75; 29,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 8,74</t>
+          <t>1,4; 8,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,76; 16,06</t>
+          <t>5,97; 15,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,98; 18,04</t>
+          <t>7,06; 17,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,83; 22,19</t>
+          <t>13,86; 22,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,1</t>
+          <t>0,67; 4,08</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,16; 10,87</t>
+          <t>5,38; 11,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,78; 12,02</t>
+          <t>5,69; 12,03</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,47; 23,46</t>
+          <t>17,0; 24,4</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,23</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,47; 13,2</t>
+          <t>5,41; 13,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,44; 10,77</t>
+          <t>4,37; 10,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,95; 37,74</t>
+          <t>26,6; 37,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 9,23</t>
+          <t>1,5; 8,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,6; 20,22</t>
+          <t>9,51; 21,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,57; 20,23</t>
+          <t>9,44; 19,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,06; 23,88</t>
+          <t>15,88; 24,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,1</t>
+          <t>0,71; 4,47</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,47; 15,03</t>
+          <t>8,68; 14,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,64; 13,52</t>
+          <t>7,3; 13,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,88; 29,53</t>
+          <t>22,59; 29,58</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,7</t>
+          <t>0,0; 4,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,59; 12,12</t>
+          <t>3,46; 12,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,5; 10,99</t>
+          <t>3,37; 11,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26,13; 38,48</t>
+          <t>26,23; 38,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,12; 12,94</t>
+          <t>3,1; 11,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,46; 20,65</t>
+          <t>9,27; 21,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,84; 16,32</t>
+          <t>6,0; 17,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 25,53</t>
+          <t>18,28; 28,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 6,2</t>
+          <t>1,76; 6,3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,25; 14,52</t>
+          <t>6,85; 14,65</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,24; 11,49</t>
+          <t>5,31; 11,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,94; 30,08</t>
+          <t>24,18; 32,7</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,68</t>
+          <t>0,45; 3,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,98; 9,22</t>
+          <t>2,81; 9,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,21; 10,18</t>
+          <t>4,05; 10,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,34; 39,76</t>
+          <t>30,39; 41,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 9,0</t>
+          <t>2,24; 8,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,14; 18,21</t>
+          <t>8,73; 17,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,26; 24,95</t>
+          <t>14,84; 25,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,47; 26,98</t>
+          <t>18,7; 26,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 5,12</t>
+          <t>1,59; 5,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,55; 12,1</t>
+          <t>6,57; 11,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,49; 16,53</t>
+          <t>10,19; 16,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,07; 31,66</t>
+          <t>25,6; 32,12</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,86</t>
+          <t>0,37; 1,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 8,84</t>
+          <t>5,1; 8,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,98; 8,42</t>
+          <t>5,02; 8,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27,09; 33,02</t>
+          <t>27,97; 33,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,8</t>
+          <t>3,25; 6,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,42; 15,87</t>
+          <t>10,59; 15,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,25; 17,91</t>
+          <t>12,05; 17,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,34; 21,68</t>
+          <t>18,69; 23,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,71</t>
+          <t>1,8; 3,56</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,13; 11,32</t>
+          <t>8,15; 11,23</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,88; 11,91</t>
+          <t>8,79; 11,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,67; 26,29</t>
+          <t>24,34; 28,08</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39261</t>
+          <t>45020</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29568</t>
+          <t>32015</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>68828</t>
+          <t>77035</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4008</t>
+          <t>0; 5972</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6833; 21040</t>
+          <t>6655; 21721</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5337; 20230</t>
+          <t>5675; 20791</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29963; 48650</t>
+          <t>34895; 57868</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1805; 11075</t>
+          <t>1779; 10886</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9456; 26344</t>
+          <t>9799; 26040</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10413; 26896</t>
+          <t>10525; 26229</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23524; 37743</t>
+          <t>25136; 40340</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2091; 12220</t>
+          <t>1991; 12161</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19379; 40809</t>
+          <t>20190; 41917</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19579; 40695</t>
+          <t>19264; 40752</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>57666; 82135</t>
+          <t>64229; 92219</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61790</t>
+          <t>69863</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>36060</t>
+          <t>40685</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97850</t>
+          <t>110548</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4973</t>
+          <t>0; 4945</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13461; 32512</t>
+          <t>13316; 33160</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11736; 28496</t>
+          <t>11562; 28181</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51430; 74794</t>
+          <t>58404; 83307</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2318; 14156</t>
+          <t>2297; 13790</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20130; 42420</t>
+          <t>19952; 44070</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19504; 41233</t>
+          <t>19244; 39655</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27779; 44059</t>
+          <t>32305; 50065</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2880; 15412</t>
+          <t>2671; 16815</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38642; 68532</t>
+          <t>39558; 67537</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35804; 63348</t>
+          <t>34211; 62137</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>83703; 112992</t>
+          <t>95546; 125105</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64840</t>
+          <t>72472</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33210</t>
+          <t>38060</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98050</t>
+          <t>110532</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7256</t>
+          <t>0; 6971</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6061; 20444</t>
+          <t>5833; 20843</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6380; 20002</t>
+          <t>6138; 20818</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52485; 77287</t>
+          <t>59388; 86344</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3741; 15508</t>
+          <t>3713; 14152</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12513; 30543</t>
+          <t>13714; 31195</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7910; 22106</t>
+          <t>8128; 23230</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8746; 88724</t>
+          <t>29675; 46838</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4863; 16988</t>
+          <t>4837; 17263</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22945; 45969</t>
+          <t>21700; 46377</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16637; 36485</t>
+          <t>16870; 36383</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38077; 164933</t>
+          <t>94028; 127143</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>76448</t>
+          <t>82381</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>53350</t>
+          <t>58099</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>129798</t>
+          <t>140480</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>848; 6985</t>
+          <t>852; 6841</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7290; 22547</t>
+          <t>6887; 22232</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11167; 26980</t>
+          <t>10744; 27465</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>65278; 88463</t>
+          <t>70446; 96383</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3291; 15858</t>
+          <t>3953; 15614</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20512; 40878</t>
+          <t>19587; 39450</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35453; 62020</t>
+          <t>36886; 63091</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>43493; 63543</t>
+          <t>48011; 68407</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5688; 18758</t>
+          <t>5826; 19533</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30736; 56739</t>
+          <t>30834; 55846</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>53862; 84910</t>
+          <t>52337; 82880</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>114835; 145004</t>
+          <t>125079; 156940</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>242339</t>
+          <t>269735</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>152188</t>
+          <t>168859</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>394527</t>
+          <t>438594</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2795; 13718</t>
+          <t>2753; 12746</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>45583; 76997</t>
+          <t>44464; 77035</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44849; 75868</t>
+          <t>45244; 76195</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>217117; 264657</t>
+          <t>244560; 294498</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>17283; 39179</t>
+          <t>18706; 40171</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>77718; 118426</t>
+          <t>78999; 119181</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>90297; 132020</t>
+          <t>88792; 129165</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>78212; 203284</t>
+          <t>150263; 186524</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23990; 48784</t>
+          <t>23649; 46759</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>131474; 183044</t>
+          <t>131836; 181554</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>145433; 195121</t>
+          <t>144074; 193592</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>255174; 457237</t>
+          <t>408488; 471254</t>
         </is>
       </c>
     </row>
